--- a/outputs/Rice_(low_quality)_tukey_classification_matrix.xlsx
+++ b/outputs/Rice_(low_quality)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="129">
   <si>
     <t>2020 May</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Alarm</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>0%</t>
@@ -1225,13 +1228,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1452,13 +1455,13 @@
         <v>110</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1679,13 +1682,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BW4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1906,13 +1909,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -2133,13 +2136,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2360,13 +2363,13 @@
         <v>109</v>
       </c>
       <c r="BU7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2587,13 +2590,13 @@
         <v>109</v>
       </c>
       <c r="BU8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2814,13 +2817,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -3041,13 +3044,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3268,13 +3271,13 @@
         <v>109</v>
       </c>
       <c r="BU11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3495,13 +3498,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3722,13 +3725,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BW13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3949,13 +3952,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4176,13 +4179,13 @@
         <v>109</v>
       </c>
       <c r="BU15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4403,13 +4406,13 @@
         <v>109</v>
       </c>
       <c r="BU16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BW16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4630,13 +4633,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BV17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4857,13 +4860,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -5084,13 +5087,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BW19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5311,13 +5314,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5538,13 +5541,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5765,13 +5768,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BW22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5992,13 +5995,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6219,13 +6222,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6446,13 +6449,13 @@
         <v>110</v>
       </c>
       <c r="BU25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6643,19 +6646,19 @@
         <v>110</v>
       </c>
       <c r="BK26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BL26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BM26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BN26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BO26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BP26" t="s">
         <v>108</v>
@@ -6673,13 +6676,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BV26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BW26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6900,13 +6903,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7127,13 +7130,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7354,13 +7357,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BV29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7581,13 +7584,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BV30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7808,13 +7811,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -8035,13 +8038,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8262,13 +8265,13 @@
         <v>110</v>
       </c>
       <c r="BU33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BV33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8489,13 +8492,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Rice_(low_quality)_tukey_classification_matrix.xlsx
+++ b/outputs/Rice_(low_quality)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="111">
   <si>
     <t>2020 May</t>
   </si>
@@ -343,64 +343,10 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>No data</t>
   </si>
   <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>28%</t>
-  </si>
-  <si>
-    <t>24%</t>
   </si>
 </sst>
 </file>
@@ -1228,13 +1174,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1284,7 +1230,7 @@
         <v>108</v>
       </c>
       <c r="P3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q3" t="s">
         <v>108</v>
@@ -1446,22 +1392,22 @@
         <v>108</v>
       </c>
       <c r="BR3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1559,7 +1505,7 @@
         <v>108</v>
       </c>
       <c r="AF4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG4" t="s">
         <v>108</v>
@@ -1592,7 +1538,7 @@
         <v>108</v>
       </c>
       <c r="AQ4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR4" t="s">
         <v>108</v>
@@ -1682,13 +1628,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BW4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1909,13 +1855,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -2136,13 +2082,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2273,7 +2219,7 @@
         <v>108</v>
       </c>
       <c r="AQ7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR7" t="s">
         <v>108</v>
@@ -2360,16 +2306,16 @@
         <v>108</v>
       </c>
       <c r="BT7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2587,16 +2533,16 @@
         <v>108</v>
       </c>
       <c r="BT8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2817,13 +2763,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2948,7 +2894,7 @@
         <v>108</v>
       </c>
       <c r="AO10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP10" t="s">
         <v>108</v>
@@ -3044,13 +2990,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3250,34 +3196,34 @@
         <v>108</v>
       </c>
       <c r="BN11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BO11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BP11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW11" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3498,13 +3444,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3596,31 +3542,31 @@
         <v>108</v>
       </c>
       <c r="AD13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK13" t="s">
         <v>108</v>
       </c>
       <c r="AL13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM13" t="s">
         <v>108</v>
@@ -3725,13 +3671,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BV13" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BW13" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3880,7 +3826,7 @@
         <v>108</v>
       </c>
       <c r="AW14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AX14" t="s">
         <v>108</v>
@@ -3952,13 +3898,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4080,10 +4026,10 @@
         <v>108</v>
       </c>
       <c r="AN15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP15" t="s">
         <v>108</v>
@@ -4170,22 +4116,22 @@
         <v>108</v>
       </c>
       <c r="BR15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BS15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV15" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW15" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4307,7 +4253,7 @@
         <v>108</v>
       </c>
       <c r="AN16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO16" t="s">
         <v>108</v>
@@ -4397,22 +4343,22 @@
         <v>108</v>
       </c>
       <c r="BR16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV16" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BW16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4513,52 +4459,52 @@
         <v>108</v>
       </c>
       <c r="AG17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW17" t="s">
         <v>108</v>
@@ -4633,13 +4579,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BV17" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW17" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4731,7 +4677,7 @@
         <v>108</v>
       </c>
       <c r="AD18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE18" t="s">
         <v>108</v>
@@ -4860,13 +4806,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4967,7 +4913,7 @@
         <v>108</v>
       </c>
       <c r="AG19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH19" t="s">
         <v>108</v>
@@ -4994,13 +4940,13 @@
         <v>108</v>
       </c>
       <c r="AP19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS19" t="s">
         <v>108</v>
@@ -5018,25 +4964,25 @@
         <v>108</v>
       </c>
       <c r="AX19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AZ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BB19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BC19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BD19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BE19" t="s">
         <v>108</v>
@@ -5051,13 +4997,13 @@
         <v>108</v>
       </c>
       <c r="BI19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BJ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BK19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BL19" t="s">
         <v>108</v>
@@ -5087,13 +5033,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV19" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BW19" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5191,7 +5137,7 @@
         <v>108</v>
       </c>
       <c r="AF20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG20" t="s">
         <v>108</v>
@@ -5314,13 +5260,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5367,16 +5313,16 @@
         <v>108</v>
       </c>
       <c r="O21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S21" t="s">
         <v>108</v>
@@ -5541,13 +5487,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW21" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5633,7 +5579,7 @@
         <v>108</v>
       </c>
       <c r="AB22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC22" t="s">
         <v>108</v>
@@ -5762,19 +5708,19 @@
         <v>108</v>
       </c>
       <c r="BS22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT22" t="s">
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV22" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BW22" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5812,7 +5758,7 @@
         <v>108</v>
       </c>
       <c r="L23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M23" t="s">
         <v>108</v>
@@ -5995,13 +5941,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6222,13 +6168,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6311,7 +6257,7 @@
         <v>108</v>
       </c>
       <c r="AA25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB25" t="s">
         <v>108</v>
@@ -6446,16 +6392,16 @@
         <v>108</v>
       </c>
       <c r="BT25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW25" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6571,94 +6517,94 @@
         <v>108</v>
       </c>
       <c r="AL26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AU26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AV26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AW26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AY26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BA26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BC26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BE26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BF26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BG26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BH26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BI26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BJ26" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK26" t="s">
         <v>109</v>
       </c>
-      <c r="AM26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AN26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AO26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AP26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AQ26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AR26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AS26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AT26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AU26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AV26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AW26" t="s">
-        <v>108</v>
-      </c>
-      <c r="AX26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AY26" t="s">
-        <v>110</v>
-      </c>
-      <c r="AZ26" t="s">
-        <v>110</v>
-      </c>
-      <c r="BA26" t="s">
-        <v>110</v>
-      </c>
-      <c r="BB26" t="s">
-        <v>110</v>
-      </c>
-      <c r="BC26" t="s">
-        <v>110</v>
-      </c>
-      <c r="BD26" t="s">
-        <v>110</v>
-      </c>
-      <c r="BE26" t="s">
+      <c r="BL26" t="s">
         <v>109</v>
       </c>
-      <c r="BF26" t="s">
-        <v>108</v>
-      </c>
-      <c r="BG26" t="s">
-        <v>108</v>
-      </c>
-      <c r="BH26" t="s">
-        <v>108</v>
-      </c>
-      <c r="BI26" t="s">
-        <v>108</v>
-      </c>
-      <c r="BJ26" t="s">
-        <v>110</v>
-      </c>
-      <c r="BK26" t="s">
-        <v>111</v>
-      </c>
-      <c r="BL26" t="s">
-        <v>111</v>
-      </c>
       <c r="BM26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BN26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BO26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BP26" t="s">
         <v>108</v>
@@ -6676,13 +6622,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BV26" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BW26" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6903,13 +6849,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -6995,7 +6941,7 @@
         <v>108</v>
       </c>
       <c r="AB28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC28" t="s">
         <v>108</v>
@@ -7130,13 +7076,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV28" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW28" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7234,55 +7180,55 @@
         <v>108</v>
       </c>
       <c r="AF29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK29" t="s">
         <v>108</v>
       </c>
       <c r="AL29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW29" t="s">
         <v>108</v>
@@ -7357,13 +7303,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BV29" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW29" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7461,55 +7407,55 @@
         <v>108</v>
       </c>
       <c r="AF30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW30" t="s">
         <v>108</v>
@@ -7584,13 +7530,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV30" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW30" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7811,13 +7757,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7945,7 +7891,7 @@
         <v>108</v>
       </c>
       <c r="AP32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ32" t="s">
         <v>108</v>
@@ -8038,13 +7984,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV32" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW32" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8157,31 +8103,31 @@
         <v>108</v>
       </c>
       <c r="AK33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT33" t="s">
         <v>108</v>
@@ -8193,10 +8139,10 @@
         <v>108</v>
       </c>
       <c r="AW33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY33" t="s">
         <v>108</v>
@@ -8253,25 +8199,25 @@
         <v>108</v>
       </c>
       <c r="BQ33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="BV33" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW33" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8330,13 +8276,13 @@
         <v>108</v>
       </c>
       <c r="S34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T34" t="s">
         <v>108</v>
       </c>
       <c r="U34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V34" t="s">
         <v>108</v>
@@ -8408,13 +8354,13 @@
         <v>108</v>
       </c>
       <c r="AS34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV34" t="s">
         <v>108</v>
@@ -8492,13 +8438,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV34" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW34" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Rice_(low_quality)_tukey_classification_matrix.xlsx
+++ b/outputs/Rice_(low_quality)_tukey_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
